--- a/data/trans_dic/P37A$medicoedad-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoedad-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 18,26</t>
+          <t>13,51; 17,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,69; 27,16</t>
+          <t>21,5; 27,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,3; 27,25</t>
+          <t>21,59; 27,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,14; 38,45</t>
+          <t>29,26; 36,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,36; 23,63</t>
+          <t>19,26; 23,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,44; 25,96</t>
+          <t>21,25; 26,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,68; 29,92</t>
+          <t>23,49; 29,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,9; 46,21</t>
+          <t>40,23; 45,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 20,69</t>
+          <t>17,44; 20,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 25,8</t>
+          <t>22,1; 25,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,66; 28,02</t>
+          <t>23,47; 27,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,83; 42,2</t>
+          <t>36,78; 41,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,73</t>
+          <t>1,35; 2,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,11</t>
+          <t>2,43; 4,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,9</t>
+          <t>4,0; 5,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,65</t>
+          <t>7,41; 9,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,66</t>
+          <t>1,23; 2,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,69</t>
+          <t>1,9; 3,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,26</t>
+          <t>4,05; 6,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,18; 37,7</t>
+          <t>7,85; 9,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,41</t>
+          <t>1,43; 2,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,58</t>
+          <t>2,41; 3,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,7</t>
+          <t>4,31; 5,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 26,58</t>
+          <t>7,86; 9,24</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,46</t>
+          <t>1,66; 5,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,6</t>
+          <t>2,58; 6,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,34</t>
+          <t>9,85; 14,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,3</t>
+          <t>1,98; 5,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,54</t>
+          <t>0,43; 2,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,52</t>
+          <t>1,26; 4,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,36</t>
+          <t>6,48; 9,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,03</t>
+          <t>1,86; 4,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,4</t>
+          <t>1,39; 3,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,58</t>
+          <t>2,35; 4,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 11,04</t>
+          <t>8,58; 11,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,13</t>
+          <t>5,55; 7,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 10,19</t>
+          <t>8,21; 10,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 10,01</t>
+          <t>8,12; 10,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,62</t>
+          <t>12,16; 14,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,78; 10,77</t>
+          <t>8,7; 10,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 11,35</t>
+          <t>9,25; 11,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 11,84</t>
+          <t>9,66; 11,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,61; 35,6</t>
+          <t>15,26; 17,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,79</t>
+          <t>7,37; 8,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 10,49</t>
+          <t>9,09; 10,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 10,69</t>
+          <t>9,21; 10,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 25,58</t>
+          <t>14,0; 15,3</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179546</t>
+          <t>190432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>329907</t>
+          <t>353487</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>509453</t>
+          <t>543918</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>142525; 188348</t>
+          <t>139423; 183712</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>211418; 264739</t>
+          <t>209565; 266385</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160675; 205550</t>
+          <t>162899; 207582</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>160338; 198019</t>
+          <t>169299; 212499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>254645; 310706</t>
+          <t>253294; 313898</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>286792; 347295</t>
+          <t>284334; 350507</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>235547; 297578</t>
+          <t>233608; 292811</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>308990; 349123</t>
+          <t>330673; 375043</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>411866; 485509</t>
+          <t>409367; 484980</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>509530; 596696</t>
+          <t>510978; 595794</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>413827; 490157</t>
+          <t>410533; 483711</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>480628; 536178</t>
+          <t>515143; 575430</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167968</t>
+          <t>186192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>377207</t>
+          <t>190578</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>545175</t>
+          <t>376770</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21481; 46266</t>
+          <t>22837; 46561</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47875; 80677</t>
+          <t>47762; 81270</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81823; 122599</t>
+          <t>82970; 122636</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117124; 198145</t>
+          <t>165191; 208692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19528; 42183</t>
+          <t>19582; 42860</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34774; 64805</t>
+          <t>33415; 62686</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81484; 124418</t>
+          <t>80429; 126220</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>182948; 843551</t>
+          <t>170473; 210517</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46505; 79108</t>
+          <t>47076; 79110</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88914; 133317</t>
+          <t>89709; 133392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>173295; 231790</t>
+          <t>175342; 232800</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>339049; 1203667</t>
+          <t>345785; 406804</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76771</t>
+          <t>84688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49732</t>
+          <t>57621</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>126504</t>
+          <t>142309</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6595; 22046</t>
+          <t>6599; 22045</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8093; 26286</t>
+          <t>8004; 25697</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14873; 36082</t>
+          <t>14084; 34473</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63452; 92757</t>
+          <t>70101; 101389</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8752; 25227</t>
+          <t>9420; 25460</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2051; 11656</t>
+          <t>1953; 11489</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7078; 24827</t>
+          <t>6935; 25336</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40696; 61839</t>
+          <t>47584; 69632</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18656; 41471</t>
+          <t>19087; 41441</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11994; 31977</t>
+          <t>13031; 32264</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24747; 50239</t>
+          <t>25794; 53327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>109564; 144327</t>
+          <t>124119; 164378</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>424286</t>
+          <t>461312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>756846</t>
+          <t>601686</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1181132</t>
+          <t>1062997</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>182065; 233678</t>
+          <t>181837; 233155</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>283304; 348494</t>
+          <t>280657; 351348</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>277185; 337935</t>
+          <t>274129; 340085</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>328285; 470012</t>
+          <t>427984; 498922</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>296561; 363853</t>
+          <t>294153; 367029</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>331402; 403426</t>
+          <t>328922; 405319</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>340186; 418339</t>
+          <t>341031; 421304</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>570412; 1300691</t>
+          <t>568795; 640427</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>494405; 585031</t>
+          <t>490841; 585437</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>633358; 731888</t>
+          <t>633702; 738847</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>638802; 738899</t>
+          <t>636296; 736310</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>973924; 1817935</t>
+          <t>1014733; 1109259</t>
         </is>
       </c>
     </row>
